--- a/menu-santaana.xlsx
+++ b/menu-santaana.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ce128a5e94e8105/Documents/Panadería Golconda/Menús/Menú en línea/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="66" documentId="11_284323B7179BCE7EC29A83AAEA162C28D842675C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0CC6A0A-8394-4435-B0F9-4741A1162E8B}"/>
+  <xr:revisionPtr revIDLastSave="67" documentId="11_284323B7179BCE7EC29A83AAEA162C28D842675C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B763D709-BEF1-4ECF-BB74-FFDB6B5013FE}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Menú" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="76">
   <si>
     <t>Día</t>
   </si>
@@ -228,6 +228,27 @@
   </si>
   <si>
     <t>Arroz con caraota</t>
+  </si>
+  <si>
+    <t>27 jul</t>
+  </si>
+  <si>
+    <t>28 jul</t>
+  </si>
+  <si>
+    <t>29 jul</t>
+  </si>
+  <si>
+    <t>30 jul</t>
+  </si>
+  <si>
+    <t>31 jul</t>
+  </si>
+  <si>
+    <t>1 ago</t>
+  </si>
+  <si>
+    <t>2 ago</t>
   </si>
 </sst>
 </file>
@@ -333,7 +354,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -351,6 +372,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -638,7 +663,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -672,8 +697,8 @@
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="8">
-        <v>46230</v>
+      <c r="B2" s="8" t="s">
+        <v>69</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>9</v>
@@ -688,8 +713,8 @@
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="8">
-        <v>46230</v>
+      <c r="B3" s="8" t="s">
+        <v>69</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>9</v>
@@ -704,8 +729,8 @@
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="8">
-        <v>46230</v>
+      <c r="B4" s="8" t="s">
+        <v>69</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>9</v>
@@ -720,8 +745,8 @@
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="8">
-        <v>46230</v>
+      <c r="B5" s="8" t="s">
+        <v>69</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>9</v>
@@ -736,8 +761,8 @@
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="8">
-        <v>46230</v>
+      <c r="B6" s="8" t="s">
+        <v>69</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>9</v>
@@ -752,8 +777,8 @@
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="8">
-        <v>46231</v>
+      <c r="B7" s="8" t="s">
+        <v>70</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>9</v>
@@ -768,8 +793,8 @@
       <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="8">
-        <v>46231</v>
+      <c r="B8" s="8" t="s">
+        <v>70</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>9</v>
@@ -784,8 +809,8 @@
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="8">
-        <v>46231</v>
+      <c r="B9" s="8" t="s">
+        <v>70</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>9</v>
@@ -800,8 +825,8 @@
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="8">
-        <v>46231</v>
+      <c r="B10" s="8" t="s">
+        <v>70</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>9</v>
@@ -816,8 +841,8 @@
       <c r="A11" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="8">
-        <v>46231</v>
+      <c r="B11" s="8" t="s">
+        <v>70</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>9</v>
@@ -832,8 +857,8 @@
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="8">
-        <v>46232</v>
+      <c r="B12" s="8" t="s">
+        <v>71</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>9</v>
@@ -848,8 +873,8 @@
       <c r="A13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="8">
-        <v>46232</v>
+      <c r="B13" s="8" t="s">
+        <v>71</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>9</v>
@@ -864,8 +889,8 @@
       <c r="A14" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="8">
-        <v>46232</v>
+      <c r="B14" s="8" t="s">
+        <v>71</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>9</v>
@@ -880,8 +905,8 @@
       <c r="A15" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B15" s="8">
-        <v>46232</v>
+      <c r="B15" s="8" t="s">
+        <v>71</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>9</v>
@@ -896,8 +921,8 @@
       <c r="A16" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="8">
-        <v>46232</v>
+      <c r="B16" s="8" t="s">
+        <v>71</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>9</v>
@@ -912,8 +937,8 @@
       <c r="A17" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="8">
-        <v>46233</v>
+      <c r="B17" s="8" t="s">
+        <v>71</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>9</v>
@@ -928,8 +953,8 @@
       <c r="A18" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B18" s="8">
-        <v>46233</v>
+      <c r="B18" s="8" t="s">
+        <v>71</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>9</v>
@@ -944,8 +969,8 @@
       <c r="A19" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="8">
-        <v>46233</v>
+      <c r="B19" s="8" t="s">
+        <v>71</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>9</v>
@@ -960,8 +985,8 @@
       <c r="A20" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="8">
-        <v>46233</v>
+      <c r="B20" s="8" t="s">
+        <v>71</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>9</v>
@@ -976,8 +1001,8 @@
       <c r="A21" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B21" s="8">
-        <v>46233</v>
+      <c r="B21" s="8" t="s">
+        <v>71</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>9</v>
@@ -992,8 +1017,8 @@
       <c r="A22" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B22" s="8">
-        <v>46234</v>
+      <c r="B22" s="8" t="s">
+        <v>72</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>9</v>
@@ -1008,8 +1033,8 @@
       <c r="A23" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="8">
-        <v>46234</v>
+      <c r="B23" s="8" t="s">
+        <v>72</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>9</v>
@@ -1024,8 +1049,8 @@
       <c r="A24" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B24" s="8">
-        <v>46234</v>
+      <c r="B24" s="8" t="s">
+        <v>72</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>9</v>
@@ -1040,8 +1065,8 @@
       <c r="A25" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="8">
-        <v>46234</v>
+      <c r="B25" s="8" t="s">
+        <v>72</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>9</v>
@@ -1056,8 +1081,8 @@
       <c r="A26" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B26" s="8">
-        <v>46234</v>
+      <c r="B26" s="8" t="s">
+        <v>72</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>9</v>
@@ -1072,8 +1097,8 @@
       <c r="A27" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B27" s="8">
-        <v>46235</v>
+      <c r="B27" s="8" t="s">
+        <v>73</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>9</v>
@@ -1092,8 +1117,8 @@
       <c r="A28" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B28" s="8">
-        <v>46235</v>
+      <c r="B28" s="8" t="s">
+        <v>73</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>9</v>
@@ -1110,8 +1135,8 @@
       <c r="A29" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B29" s="8">
-        <v>46235</v>
+      <c r="B29" s="8" t="s">
+        <v>73</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>9</v>
@@ -1128,8 +1153,8 @@
       <c r="A30" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B30" s="8">
-        <v>46235</v>
+      <c r="B30" s="8" t="s">
+        <v>73</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>9</v>
@@ -1146,8 +1171,8 @@
       <c r="A31" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B31" s="8">
-        <v>46235</v>
+      <c r="B31" s="8" t="s">
+        <v>73</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>9</v>
@@ -1164,8 +1189,8 @@
       <c r="A32" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B32" s="8">
-        <v>46235</v>
+      <c r="B32" s="8" t="s">
+        <v>74</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>9</v>
@@ -1184,8 +1209,8 @@
       <c r="A33" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B33" s="8">
-        <v>46235</v>
+      <c r="B33" s="8" t="s">
+        <v>74</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>9</v>
@@ -1202,8 +1227,8 @@
       <c r="A34" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B34" s="8">
-        <v>46235</v>
+      <c r="B34" s="8" t="s">
+        <v>74</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>9</v>
@@ -1220,8 +1245,8 @@
       <c r="A35" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B35" s="8">
-        <v>46235</v>
+      <c r="B35" s="8" t="s">
+        <v>74</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>9</v>
@@ -1238,8 +1263,8 @@
       <c r="A36" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B36" s="8">
-        <v>46236</v>
+      <c r="B36" s="8" t="s">
+        <v>74</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>9</v>
@@ -1256,8 +1281,8 @@
       <c r="A37" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B37" s="8">
-        <v>46236</v>
+      <c r="B37" s="8" t="s">
+        <v>74</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>9</v>
@@ -1272,8 +1297,8 @@
       <c r="A38" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B38" s="8">
-        <v>46236</v>
+      <c r="B38" s="8" t="s">
+        <v>74</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>9</v>
@@ -1288,8 +1313,8 @@
       <c r="A39" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B39" s="8">
-        <v>46236</v>
+      <c r="B39" s="8" t="s">
+        <v>74</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>9</v>
@@ -1304,8 +1329,8 @@
       <c r="A40" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B40" s="8">
-        <v>46236</v>
+      <c r="B40" s="8" t="s">
+        <v>74</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>9</v>
@@ -1315,6 +1340,31 @@
         <v>68</v>
       </c>
       <c r="F40" s="4"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B41" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B42" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B43" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B44" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B45" s="8" t="s">
+        <v>75</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="3">

--- a/menu-santaana.xlsx
+++ b/menu-santaana.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ce128a5e94e8105/Documents/Panadería Golconda/Menús/Menú en línea/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="67" documentId="11_284323B7179BCE7EC29A83AAEA162C28D842675C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B763D709-BEF1-4ECF-BB74-FFDB6B5013FE}"/>
+  <xr:revisionPtr revIDLastSave="138" documentId="11_284323B7179BCE7EC29A83AAEA162C28D842675C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3AF87544-AEE2-4002-921A-AAE262B84F82}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Menú" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="76">
   <si>
     <t>Día</t>
   </si>
@@ -59,9 +59,6 @@
     <t>Jueves</t>
   </si>
   <si>
-    <t>Arroz a las finas hierbas</t>
-  </si>
-  <si>
     <t>Viernes</t>
   </si>
   <si>
@@ -140,122 +137,125 @@
     <t>No cambies los títulos de la fila 1 ni el nombre de la hoja «Menú».</t>
   </si>
   <si>
-    <t>Sopa de cuchuco de trigo</t>
-  </si>
-  <si>
-    <t>Chuleta de cerdo apanada</t>
-  </si>
-  <si>
-    <t>Yuca dorada</t>
-  </si>
-  <si>
-    <t>Sopa de arroz con menudencias</t>
-  </si>
-  <si>
-    <t>Lasaña mixta de pollo y boloñesa</t>
-  </si>
-  <si>
-    <t>Pan francés con ajo</t>
-  </si>
-  <si>
     <t>Ensalada tropical</t>
   </si>
   <si>
-    <t>Papa crisper</t>
-  </si>
-  <si>
-    <t>Crema de cebolla</t>
-  </si>
-  <si>
-    <t>Pollo a la naranja</t>
-  </si>
-  <si>
-    <t>Papa smile</t>
-  </si>
-  <si>
-    <t>Soufflé de berenjena</t>
-  </si>
-  <si>
-    <t>Arroz al perejil</t>
-  </si>
-  <si>
-    <t>Sopa de lentejas</t>
-  </si>
-  <si>
-    <t>Bolitas de res en salsa napolitana</t>
-  </si>
-  <si>
-    <t>Torta de zanahoria</t>
-  </si>
-  <si>
-    <t>Ensalada de tomate, pepino cohombro y zuccinni a la vinagreta</t>
-  </si>
-  <si>
-    <t>Sopa de mazamorra chiquita</t>
-  </si>
-  <si>
-    <t>Alitas de pollo a la broaster</t>
-  </si>
-  <si>
-    <t>Papa alemana</t>
-  </si>
-  <si>
-    <t>Ensalada de pepino cohombro con yogurt</t>
-  </si>
-  <si>
     <t>Arroz con hilos de espinaca</t>
   </si>
   <si>
-    <t>Puré de papa mixto</t>
-  </si>
-  <si>
-    <t>Ensalada veraniega</t>
-  </si>
-  <si>
-    <t>Sopa de conchitas</t>
-  </si>
-  <si>
-    <t>Conchitas de pasta</t>
-  </si>
-  <si>
-    <t>Carne desmechada</t>
-  </si>
-  <si>
     <t>Patacón</t>
   </si>
   <si>
-    <t>Ensalada a la huerta</t>
-  </si>
-  <si>
-    <t>Arroz con caraota</t>
-  </si>
-  <si>
-    <t>27 jul</t>
-  </si>
-  <si>
-    <t>28 jul</t>
-  </si>
-  <si>
-    <t>29 jul</t>
-  </si>
-  <si>
-    <t>30 jul</t>
-  </si>
-  <si>
-    <t>31 jul</t>
-  </si>
-  <si>
-    <t>1 ago</t>
-  </si>
-  <si>
-    <t>2 ago</t>
+    <t>3 ago</t>
+  </si>
+  <si>
+    <t>4 ago</t>
+  </si>
+  <si>
+    <t>5 ago</t>
+  </si>
+  <si>
+    <t>6 ago</t>
+  </si>
+  <si>
+    <t>7 ago</t>
+  </si>
+  <si>
+    <t>8 ago</t>
+  </si>
+  <si>
+    <t>9 ago</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>Sopa de cebada perlada</t>
+  </si>
+  <si>
+    <t>Carne al vino</t>
+  </si>
+  <si>
+    <t>Croquetas de papa</t>
+  </si>
+  <si>
+    <t>Ensalada waldorf</t>
+  </si>
+  <si>
+    <t>Arroz verde</t>
+  </si>
+  <si>
+    <t>Sopa de avena</t>
+  </si>
+  <si>
+    <t>Pollo en salsa provenzal</t>
+  </si>
+  <si>
+    <t>Papa richie al horno</t>
+  </si>
+  <si>
+    <t>Ensalada zuchinni</t>
+  </si>
+  <si>
+    <t>Arroz con quinoa</t>
+  </si>
+  <si>
+    <t>Mondongo</t>
+  </si>
+  <si>
+    <t>Sopa de maíz pintado</t>
+  </si>
+  <si>
+    <t>Crema de zanahoria</t>
+  </si>
+  <si>
+    <t>Pollo oriental en salsa de mango</t>
+  </si>
+  <si>
+    <t>Copitos de papa con ajonjolí</t>
+  </si>
+  <si>
+    <t>Ensalada mediterránea</t>
+  </si>
+  <si>
+    <t>Arroz al cebollín</t>
+  </si>
+  <si>
+    <t>Sopa de patacón</t>
+  </si>
+  <si>
+    <t>Filete de mojarra crunch con salsa tártara</t>
+  </si>
+  <si>
+    <t>Ensalada rusa</t>
+  </si>
+  <si>
+    <t>Tomate, aguacate y zuchinni a la vinagreta</t>
+  </si>
+  <si>
+    <t>Arroz con coco</t>
+  </si>
+  <si>
+    <t>Torta de banano</t>
+  </si>
+  <si>
+    <t>Ensalada arcoiris</t>
+  </si>
+  <si>
+    <t>Sopa de macarrones</t>
+  </si>
+  <si>
+    <t>Pollo tropical</t>
+  </si>
+  <si>
+    <t>Dedito de queso mozarella</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -289,6 +289,12 @@
       <color rgb="FF4A3524"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -663,7 +669,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -698,14 +704,14 @@
         <v>6</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="4" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="F2" s="4"/>
     </row>
@@ -714,14 +720,14 @@
         <v>6</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="4" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F3" s="4"/>
     </row>
@@ -730,14 +736,14 @@
         <v>6</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="4" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="F4" s="4"/>
     </row>
@@ -746,14 +752,14 @@
         <v>6</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="4" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="F5" s="4"/>
     </row>
@@ -762,14 +768,14 @@
         <v>6</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="4" t="s">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="F6" s="4"/>
     </row>
@@ -778,14 +784,14 @@
         <v>8</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="4" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F7" s="4"/>
     </row>
@@ -794,14 +800,14 @@
         <v>8</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="4" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="F8" s="4"/>
     </row>
@@ -810,14 +816,14 @@
         <v>8</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="4" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="F9" s="4"/>
     </row>
@@ -826,14 +832,14 @@
         <v>8</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="4" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F10" s="4"/>
     </row>
@@ -842,14 +848,14 @@
         <v>8</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="4" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="F11" s="4"/>
     </row>
@@ -858,14 +864,16 @@
         <v>10</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="3"/>
+      <c r="D12" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="E12" s="4" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="F12" s="4"/>
     </row>
@@ -874,14 +882,16 @@
         <v>10</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="3"/>
+      <c r="D13" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="E13" s="4" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="F13" s="4"/>
     </row>
@@ -890,14 +900,16 @@
         <v>10</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3"/>
+      <c r="D14" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="E14" s="4" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="F14" s="4"/>
     </row>
@@ -906,14 +918,16 @@
         <v>10</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="3"/>
+      <c r="D15" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="E15" s="4" t="s">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="F15" s="4"/>
     </row>
@@ -922,78 +936,90 @@
         <v>10</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D16" s="3"/>
+      <c r="D16" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="E16" s="4" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="F16" s="4"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D17" s="3"/>
+      <c r="D17" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="E17" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F17" s="4"/>
+        <v>22</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D18" s="3"/>
+      <c r="D18" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="E18" s="4" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="F18" s="4"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D19" s="3"/>
+      <c r="D19" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="E19" s="4" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="F19" s="4"/>
     </row>
-    <row r="20" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="3"/>
+      <c r="D20" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="E20" s="4" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="F20" s="4"/>
     </row>
@@ -1002,379 +1028,432 @@
         <v>11</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="4" t="s">
-        <v>12</v>
+        <v>61</v>
       </c>
       <c r="F21" s="4"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="4" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F22" s="4"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="4" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F23" s="4"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="4" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F24" s="4"/>
     </row>
-    <row r="25" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="4" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F25" s="4"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="4" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F26" s="4"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>16</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="D27" s="3"/>
       <c r="E27" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>18</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="F27" s="4"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>16</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="D28" s="3"/>
       <c r="E28" s="4" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="F28" s="4"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>16</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="D29" s="3"/>
       <c r="E29" s="4" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="F29" s="4"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>16</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="D30" s="3"/>
       <c r="E30" s="4" t="s">
-        <v>7</v>
+        <v>70</v>
       </c>
       <c r="F30" s="4"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B31" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>21</v>
-      </c>
       <c r="E31" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F31" s="4"/>
+        <v>16</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B32" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>21</v>
-      </c>
       <c r="E32" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>24</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="F32" s="4"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B33" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>21</v>
-      </c>
       <c r="E33" s="4" t="s">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="F33" s="4"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B34" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>21</v>
-      </c>
       <c r="E34" s="4" t="s">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="F34" s="4"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E35" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>7</v>
       </c>
       <c r="F35" s="4"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D36" s="3"/>
+      <c r="D36" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="E36" s="4" t="s">
-        <v>63</v>
+        <v>22</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D37" s="3"/>
+      <c r="D37" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="E37" s="4" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F37" s="4"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D38" s="3"/>
+      <c r="D38" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="E38" s="4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F38" s="4"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D39" s="3"/>
+      <c r="D39" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="E39" s="4" t="s">
-        <v>67</v>
+        <v>7</v>
       </c>
       <c r="F39" s="4"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="D40" s="3"/>
       <c r="E40" s="4" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F40" s="4"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="B41" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D41" s="3"/>
+      <c r="E41" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F41" s="4"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D42" s="3"/>
+      <c r="E42" s="4" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B42" s="8" t="s">
-        <v>75</v>
-      </c>
+      <c r="F42" s="4"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="B43" s="8" t="s">
-        <v>75</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D43" s="3"/>
+      <c r="E43" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F43" s="4"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="B44" s="8" t="s">
-        <v>75</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D44" s="3"/>
+      <c r="E44" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F44" s="4"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B45" s="8" t="s">
-        <v>75</v>
-      </c>
+      <c r="B45" s="8"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B46" s="8"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B47" s="8"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B48" s="8"/>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B49" s="8"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="A2:A400" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="A2:A404" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C2:C400" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C2:C404" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Sí,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D400" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D404" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Opción 1,Opción 2,Opción 3"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1392,7 +1471,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -1400,7 +1479,7 @@
     </row>
     <row r="3" spans="1:1" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -1408,32 +1487,32 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -1441,12 +1520,12 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
@@ -1454,17 +1533,17 @@
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/menu-santaana.xlsx
+++ b/menu-santaana.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ce128a5e94e8105/Documents/Panadería Golconda/Menús/Menú en línea/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="138" documentId="11_284323B7179BCE7EC29A83AAEA162C28D842675C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3AF87544-AEE2-4002-921A-AAE262B84F82}"/>
+  <xr:revisionPtr revIDLastSave="190" documentId="11_284323B7179BCE7EC29A83AAEA162C28D842675C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88DCCA46-DA69-45D8-BCB0-F193C7254A89}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Menú" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="78">
   <si>
     <t>Día</t>
   </si>
@@ -137,118 +137,124 @@
     <t>No cambies los títulos de la fila 1 ni el nombre de la hoja «Menú».</t>
   </si>
   <si>
-    <t>Ensalada tropical</t>
-  </si>
-  <si>
-    <t>Arroz con hilos de espinaca</t>
-  </si>
-  <si>
-    <t>Patacón</t>
-  </si>
-  <si>
-    <t>3 ago</t>
-  </si>
-  <si>
-    <t>4 ago</t>
-  </si>
-  <si>
-    <t>5 ago</t>
-  </si>
-  <si>
-    <t>6 ago</t>
-  </si>
-  <si>
-    <t>7 ago</t>
-  </si>
-  <si>
-    <t>8 ago</t>
-  </si>
-  <si>
-    <t>9 ago</t>
-  </si>
-  <si>
     <t>Sí</t>
   </si>
   <si>
-    <t>Sopa de cebada perlada</t>
-  </si>
-  <si>
-    <t>Carne al vino</t>
-  </si>
-  <si>
-    <t>Croquetas de papa</t>
-  </si>
-  <si>
-    <t>Ensalada waldorf</t>
-  </si>
-  <si>
-    <t>Arroz verde</t>
-  </si>
-  <si>
-    <t>Sopa de avena</t>
-  </si>
-  <si>
-    <t>Pollo en salsa provenzal</t>
-  </si>
-  <si>
-    <t>Papa richie al horno</t>
-  </si>
-  <si>
-    <t>Ensalada zuchinni</t>
-  </si>
-  <si>
-    <t>Arroz con quinoa</t>
-  </si>
-  <si>
-    <t>Mondongo</t>
-  </si>
-  <si>
     <t>Sopa de maíz pintado</t>
   </si>
   <si>
-    <t>Crema de zanahoria</t>
-  </si>
-  <si>
-    <t>Pollo oriental en salsa de mango</t>
-  </si>
-  <si>
-    <t>Copitos de papa con ajonjolí</t>
-  </si>
-  <si>
-    <t>Ensalada mediterránea</t>
-  </si>
-  <si>
-    <t>Arroz al cebollín</t>
-  </si>
-  <si>
-    <t>Sopa de patacón</t>
-  </si>
-  <si>
-    <t>Filete de mojarra crunch con salsa tártara</t>
-  </si>
-  <si>
-    <t>Ensalada rusa</t>
-  </si>
-  <si>
-    <t>Tomate, aguacate y zuchinni a la vinagreta</t>
-  </si>
-  <si>
-    <t>Arroz con coco</t>
-  </si>
-  <si>
-    <t>Torta de banano</t>
-  </si>
-  <si>
-    <t>Ensalada arcoiris</t>
-  </si>
-  <si>
-    <t>Sopa de macarrones</t>
-  </si>
-  <si>
-    <t>Pollo tropical</t>
-  </si>
-  <si>
-    <t>Dedito de queso mozarella</t>
+    <t>10 ago</t>
+  </si>
+  <si>
+    <t>Sopa de cascabeles</t>
+  </si>
+  <si>
+    <t>Muchacho relleno</t>
+  </si>
+  <si>
+    <t>En salsa de maracuyá</t>
+  </si>
+  <si>
+    <t>Papa Lyonesa</t>
+  </si>
+  <si>
+    <t>Ensalada fiorentina</t>
+  </si>
+  <si>
+    <t>Arroz al maní</t>
+  </si>
+  <si>
+    <t>11 ago</t>
+  </si>
+  <si>
+    <t>Sopa de torrejas</t>
+  </si>
+  <si>
+    <t>Soufflé de pollo y atún</t>
+  </si>
+  <si>
+    <t>Papa chip</t>
+  </si>
+  <si>
+    <t>Ensalada de huevo moscovita</t>
+  </si>
+  <si>
+    <t>12 ago</t>
+  </si>
+  <si>
+    <t>Entero</t>
+  </si>
+  <si>
+    <t>Costilla de res</t>
+  </si>
+  <si>
+    <t>Yuca, mazorca y plátano</t>
+  </si>
+  <si>
+    <t>Guacamole</t>
+  </si>
+  <si>
+    <t>Yuca o plátano</t>
+  </si>
+  <si>
+    <t>13 ago</t>
+  </si>
+  <si>
+    <t>Sopa de minestrone</t>
+  </si>
+  <si>
+    <t>Pollo mediterráneo</t>
+  </si>
+  <si>
+    <t>Papa a la griega</t>
+  </si>
+  <si>
+    <t>Ensalada cherry</t>
+  </si>
+  <si>
+    <t>Arroz al perejil</t>
+  </si>
+  <si>
+    <t>Sopa de cuchuco de cebada</t>
+  </si>
+  <si>
+    <t>Lomo de cerdo</t>
+  </si>
+  <si>
+    <t>En salsa de frutos del bosque</t>
+  </si>
+  <si>
+    <t>Papa al gratín</t>
+  </si>
+  <si>
+    <t>Ensalada verde</t>
+  </si>
+  <si>
+    <t>14 ago</t>
+  </si>
+  <si>
+    <t>15 ago</t>
+  </si>
+  <si>
+    <t>Plátano al horno</t>
+  </si>
+  <si>
+    <t>16 ago</t>
+  </si>
+  <si>
+    <t>Sopa madrileña</t>
+  </si>
+  <si>
+    <t>Steak pimienta</t>
+  </si>
+  <si>
+    <t>Tortilla española</t>
+  </si>
+  <si>
+    <t>Ensalada romana</t>
+  </si>
+  <si>
+    <t>Arroz almendrado</t>
   </si>
 </sst>
 </file>
@@ -669,7 +675,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -704,14 +710,14 @@
         <v>6</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="4" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="F2" s="4"/>
     </row>
@@ -720,30 +726,32 @@
         <v>6</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F3" s="4"/>
+        <v>42</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="4" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F4" s="4"/>
     </row>
@@ -752,14 +760,14 @@
         <v>6</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="4" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="F5" s="4"/>
     </row>
@@ -768,14 +776,14 @@
         <v>6</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="4" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="F6" s="4"/>
     </row>
@@ -784,14 +792,14 @@
         <v>8</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="4" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F7" s="4"/>
     </row>
@@ -800,14 +808,14 @@
         <v>8</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="4" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F8" s="4"/>
     </row>
@@ -816,14 +824,14 @@
         <v>8</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="4" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F9" s="4"/>
     </row>
@@ -832,14 +840,14 @@
         <v>8</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="4" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F10" s="4"/>
     </row>
@@ -848,14 +856,14 @@
         <v>8</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="4" t="s">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="F11" s="4"/>
     </row>
@@ -864,7 +872,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>9</v>
@@ -873,7 +881,7 @@
         <v>15</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="F12" s="4"/>
     </row>
@@ -882,7 +890,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>9</v>
@@ -891,7 +899,7 @@
         <v>15</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F13" s="4"/>
     </row>
@@ -900,7 +908,7 @@
         <v>10</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>9</v>
@@ -909,7 +917,7 @@
         <v>15</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="F14" s="4"/>
     </row>
@@ -918,7 +926,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>9</v>
@@ -927,7 +935,7 @@
         <v>15</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>7</v>
+        <v>56</v>
       </c>
       <c r="F15" s="4"/>
     </row>
@@ -936,16 +944,16 @@
         <v>10</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="F16" s="4"/>
     </row>
@@ -954,7 +962,7 @@
         <v>10</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>9</v>
@@ -963,18 +971,16 @@
         <v>20</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>23</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="F17" s="4"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>9</v>
@@ -983,16 +989,18 @@
         <v>20</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F18" s="4"/>
+        <v>22</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>9</v>
@@ -1001,7 +1009,7 @@
         <v>20</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="F19" s="4"/>
     </row>
@@ -1010,7 +1018,7 @@
         <v>10</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>9</v>
@@ -1019,23 +1027,25 @@
         <v>20</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>7</v>
+        <v>56</v>
       </c>
       <c r="F20" s="4"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D21" s="3"/>
+      <c r="D21" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="E21" s="4" t="s">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="F21" s="4"/>
     </row>
@@ -1044,14 +1054,14 @@
         <v>11</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F22" s="4"/>
     </row>
@@ -1060,14 +1070,14 @@
         <v>11</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F23" s="4"/>
     </row>
@@ -1076,14 +1086,14 @@
         <v>11</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F24" s="4"/>
     </row>
@@ -1092,30 +1102,30 @@
         <v>11</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F25" s="4"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F26" s="4"/>
     </row>
@@ -1124,14 +1134,14 @@
         <v>12</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F27" s="4"/>
     </row>
@@ -1140,30 +1150,32 @@
         <v>12</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F28" s="4"/>
-    </row>
-    <row r="29" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F29" s="4"/>
     </row>
@@ -1172,43 +1184,39 @@
         <v>12</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="D30" s="3"/>
       <c r="E30" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F30" s="4"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>15</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="D31" s="3"/>
       <c r="E31" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>17</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F31" s="4"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>9</v>
@@ -1217,16 +1225,18 @@
         <v>15</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F32" s="4"/>
+        <v>16</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>9</v>
@@ -1235,7 +1245,7 @@
         <v>15</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F33" s="4"/>
     </row>
@@ -1244,7 +1254,7 @@
         <v>14</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>9</v>
@@ -1253,7 +1263,7 @@
         <v>15</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="F34" s="4"/>
     </row>
@@ -1262,16 +1272,16 @@
         <v>14</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="F35" s="4"/>
     </row>
@@ -1280,7 +1290,7 @@
         <v>14</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>9</v>
@@ -1289,18 +1299,16 @@
         <v>20</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>23</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="F36" s="4"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>9</v>
@@ -1309,16 +1317,18 @@
         <v>20</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F37" s="4"/>
+        <v>22</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>9</v>
@@ -1327,7 +1337,7 @@
         <v>20</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F38" s="4"/>
     </row>
@@ -1336,7 +1346,7 @@
         <v>14</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>9</v>
@@ -1345,23 +1355,25 @@
         <v>20</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F39" s="4"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D40" s="3"/>
+        <v>9</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="E40" s="4" t="s">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="F40" s="4"/>
     </row>
@@ -1370,14 +1382,14 @@
         <v>24</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F41" s="4"/>
     </row>
@@ -1386,14 +1398,14 @@
         <v>24</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F42" s="4"/>
     </row>
@@ -1402,14 +1414,14 @@
         <v>24</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="4" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="F43" s="4"/>
     </row>
@@ -1418,19 +1430,32 @@
         <v>24</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="D44" s="3"/>
       <c r="E44" s="4" t="s">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="F44" s="4"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B45" s="8"/>
+      <c r="A45" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D45" s="3"/>
+      <c r="E45" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F45" s="4"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B46" s="8"/>
@@ -1443,17 +1468,20 @@
     </row>
     <row r="49" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B49" s="8"/>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B50" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="A2:A404" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="A2:A405" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C2:C404" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C2:C405" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Sí,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D404" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D405" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Opción 1,Opción 2,Opción 3"</formula1>
     </dataValidation>
   </dataValidations>

--- a/menu-santaana.xlsx
+++ b/menu-santaana.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ce128a5e94e8105/Documents/Panadería Golconda/Menús/Menú en línea/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="190" documentId="11_284323B7179BCE7EC29A83AAEA162C28D842675C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88DCCA46-DA69-45D8-BCB0-F193C7254A89}"/>
+  <xr:revisionPtr revIDLastSave="244" documentId="11_284323B7179BCE7EC29A83AAEA162C28D842675C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D23255B-C259-4CED-A7AB-6AE2D798FAB4}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="76">
   <si>
     <t>Día</t>
   </si>
@@ -62,9 +62,6 @@
     <t>Viernes</t>
   </si>
   <si>
-    <t>Verduras calientes</t>
-  </si>
-  <si>
     <t>Sábado</t>
   </si>
   <si>
@@ -140,121 +137,118 @@
     <t>Sí</t>
   </si>
   <si>
-    <t>Sopa de maíz pintado</t>
-  </si>
-  <si>
-    <t>10 ago</t>
-  </si>
-  <si>
-    <t>Sopa de cascabeles</t>
-  </si>
-  <si>
-    <t>Muchacho relleno</t>
-  </si>
-  <si>
     <t>En salsa de maracuyá</t>
   </si>
   <si>
-    <t>Papa Lyonesa</t>
-  </si>
-  <si>
-    <t>Ensalada fiorentina</t>
-  </si>
-  <si>
-    <t>Arroz al maní</t>
-  </si>
-  <si>
-    <t>11 ago</t>
-  </si>
-  <si>
-    <t>Sopa de torrejas</t>
-  </si>
-  <si>
-    <t>Soufflé de pollo y atún</t>
-  </si>
-  <si>
-    <t>Papa chip</t>
-  </si>
-  <si>
-    <t>Ensalada de huevo moscovita</t>
-  </si>
-  <si>
-    <t>12 ago</t>
-  </si>
-  <si>
-    <t>Entero</t>
-  </si>
-  <si>
-    <t>Costilla de res</t>
-  </si>
-  <si>
-    <t>Yuca, mazorca y plátano</t>
-  </si>
-  <si>
-    <t>Guacamole</t>
-  </si>
-  <si>
-    <t>Yuca o plátano</t>
-  </si>
-  <si>
-    <t>13 ago</t>
-  </si>
-  <si>
     <t>Sopa de minestrone</t>
   </si>
   <si>
-    <t>Pollo mediterráneo</t>
-  </si>
-  <si>
-    <t>Papa a la griega</t>
-  </si>
-  <si>
     <t>Ensalada cherry</t>
   </si>
   <si>
-    <t>Arroz al perejil</t>
-  </si>
-  <si>
-    <t>Sopa de cuchuco de cebada</t>
-  </si>
-  <si>
-    <t>Lomo de cerdo</t>
-  </si>
-  <si>
-    <t>En salsa de frutos del bosque</t>
-  </si>
-  <si>
-    <t>Papa al gratín</t>
-  </si>
-  <si>
-    <t>Ensalada verde</t>
-  </si>
-  <si>
-    <t>14 ago</t>
-  </si>
-  <si>
-    <t>15 ago</t>
-  </si>
-  <si>
-    <t>Plátano al horno</t>
-  </si>
-  <si>
-    <t>16 ago</t>
-  </si>
-  <si>
-    <t>Sopa madrileña</t>
-  </si>
-  <si>
-    <t>Steak pimienta</t>
-  </si>
-  <si>
-    <t>Tortilla española</t>
-  </si>
-  <si>
-    <t>Ensalada romana</t>
-  </si>
-  <si>
-    <t>Arroz almendrado</t>
+    <t>17 ago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crema de champiñones </t>
+  </si>
+  <si>
+    <t>Piccata de pollo</t>
+  </si>
+  <si>
+    <t>Pasta corta</t>
+  </si>
+  <si>
+    <t>Con tomates frescos</t>
+  </si>
+  <si>
+    <t>Ensalada de melón</t>
+  </si>
+  <si>
+    <t>Con vinagreta oriental</t>
+  </si>
+  <si>
+    <t>18 ago</t>
+  </si>
+  <si>
+    <t>Sopa de colicero</t>
+  </si>
+  <si>
+    <t>Churrasco a la plancha</t>
+  </si>
+  <si>
+    <t>Papa a la crema</t>
+  </si>
+  <si>
+    <t>Ensalada roja</t>
+  </si>
+  <si>
+    <t>19 ago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sopa de verduras </t>
+  </si>
+  <si>
+    <t>Pollo a la hawaiana</t>
+  </si>
+  <si>
+    <t>Ensalada irlandesa</t>
+  </si>
+  <si>
+    <t>Arroz con ajonjolí</t>
+  </si>
+  <si>
+    <t>20 ago</t>
+  </si>
+  <si>
+    <t>21 ago</t>
+  </si>
+  <si>
+    <t>22 ago</t>
+  </si>
+  <si>
+    <t>Papa smiles</t>
+  </si>
+  <si>
+    <t>Sopa de sancocho</t>
+  </si>
+  <si>
+    <t>Pulpa de cerdo a la plancha</t>
+  </si>
+  <si>
+    <t>Papa criolla dorada</t>
+  </si>
+  <si>
+    <t>Sopa de tortilla de huevo</t>
+  </si>
+  <si>
+    <t>Mojarra frita</t>
+  </si>
+  <si>
+    <t>Patacón con hogao</t>
+  </si>
+  <si>
+    <t>Ensalada con aguacate</t>
+  </si>
+  <si>
+    <t>Arroz con maicitos</t>
+  </si>
+  <si>
+    <t>Soufflé de papa</t>
+  </si>
+  <si>
+    <t>Ensalada del sol</t>
+  </si>
+  <si>
+    <t>23 ago</t>
+  </si>
+  <si>
+    <t>Pierna pernil al BBQ</t>
+  </si>
+  <si>
+    <t>Papa postiza</t>
+  </si>
+  <si>
+    <t>Ensalada César</t>
   </si>
 </sst>
 </file>
@@ -675,7 +669,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -710,14 +704,14 @@
         <v>6</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F2" s="4"/>
     </row>
@@ -726,17 +720,17 @@
         <v>6</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -744,46 +738,50 @@
         <v>6</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F4" s="4"/>
+      <c r="F4" s="4" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F5" s="4"/>
+        <v>46</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="4" t="s">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="F6" s="4"/>
     </row>
@@ -792,14 +790,14 @@
         <v>8</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F7" s="4"/>
     </row>
@@ -808,14 +806,14 @@
         <v>8</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F8" s="4"/>
     </row>
@@ -824,14 +822,14 @@
         <v>8</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F9" s="4"/>
     </row>
@@ -840,14 +838,14 @@
         <v>8</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F10" s="4"/>
     </row>
@@ -856,7 +854,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>9</v>
@@ -872,16 +870,14 @@
         <v>10</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>15</v>
-      </c>
+      <c r="D12" s="3"/>
       <c r="E12" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F12" s="4"/>
     </row>
@@ -890,16 +886,14 @@
         <v>10</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>15</v>
-      </c>
+      <c r="D13" s="3"/>
       <c r="E13" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F13" s="4"/>
     </row>
@@ -908,16 +902,14 @@
         <v>10</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>15</v>
-      </c>
+      <c r="D14" s="3"/>
       <c r="E14" s="4" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="F14" s="4"/>
     </row>
@@ -926,14 +918,12 @@
         <v>10</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>15</v>
-      </c>
+      <c r="D15" s="3"/>
       <c r="E15" s="4" t="s">
         <v>56</v>
       </c>
@@ -944,106 +934,92 @@
         <v>10</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>15</v>
-      </c>
+      <c r="D16" s="3"/>
       <c r="E16" s="4" t="s">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="F16" s="4"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>20</v>
-      </c>
+      <c r="D17" s="3"/>
       <c r="E17" s="4" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="F17" s="4"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>20</v>
-      </c>
+      <c r="D18" s="3"/>
       <c r="E18" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>23</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="F18" s="4"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>20</v>
-      </c>
+      <c r="D19" s="3"/>
       <c r="E19" s="4" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="F19" s="4"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>20</v>
-      </c>
+      <c r="D20" s="3"/>
       <c r="E20" s="4" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="F20" s="4"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>20</v>
-      </c>
+      <c r="D21" s="3"/>
       <c r="E21" s="4" t="s">
         <v>7</v>
       </c>
@@ -1051,234 +1027,244 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="4" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F22" s="4"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="4" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F23" s="4"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="4" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F24" s="4"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="4" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="F25" s="4"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="4" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F26" s="4"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D27" s="3"/>
+        <v>9</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="E27" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="F27" s="4"/>
+        <v>15</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D28" s="3"/>
+        <v>9</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="E28" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>66</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="F28" s="4"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D29" s="3"/>
+        <v>9</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="E29" s="4" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="F29" s="4"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D30" s="3"/>
+        <v>9</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="E30" s="4" t="s">
-        <v>68</v>
+        <v>7</v>
       </c>
       <c r="F30" s="4"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D31" s="3"/>
+        <v>9</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="E31" s="4" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F31" s="4"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B33" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E33" s="4" t="s">
         <v>70</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>18</v>
       </c>
       <c r="F33" s="4"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>19</v>
+        <v>71</v>
       </c>
       <c r="F34" s="4"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>7</v>
@@ -1287,201 +1273,109 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>20</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="D36" s="3"/>
       <c r="E36" s="4" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="F36" s="4"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>20</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="D37" s="3"/>
       <c r="E37" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>23</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="F37" s="4"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>20</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="D38" s="3"/>
       <c r="E38" s="4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F38" s="4"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>20</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="D39" s="3"/>
       <c r="E39" s="4" t="s">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="F39" s="4"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>20</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="D40" s="3"/>
       <c r="E40" s="4" t="s">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="F40" s="4"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B41" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D41" s="3"/>
-      <c r="E41" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="F41" s="4"/>
+      <c r="B41" s="8"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B42" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D42" s="3"/>
-      <c r="E42" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="F42" s="4"/>
+      <c r="B42" s="8"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B43" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D43" s="3"/>
-      <c r="E43" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="F43" s="4"/>
+      <c r="B43" s="8"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B44" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D44" s="3"/>
-      <c r="E44" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="F44" s="4"/>
+      <c r="B44" s="8"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B45" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D45" s="3"/>
-      <c r="E45" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="F45" s="4"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B46" s="8"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B47" s="8"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B48" s="8"/>
-    </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B49" s="8"/>
-    </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B50" s="8"/>
+      <c r="B45" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="A2:A405" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="A2:A400" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C2:C405" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C2:C400" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Sí,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D405" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D400" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Opción 1,Opción 2,Opción 3"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1499,7 +1393,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -1507,7 +1401,7 @@
     </row>
     <row r="3" spans="1:1" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -1515,32 +1409,32 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
@@ -1548,12 +1442,12 @@
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
@@ -1561,17 +1455,17 @@
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/menu-santaana.xlsx
+++ b/menu-santaana.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ce128a5e94e8105/Documents/Panadería Golconda/Menús/Menú en línea/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="244" documentId="11_284323B7179BCE7EC29A83AAEA162C28D842675C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D23255B-C259-4CED-A7AB-6AE2D798FAB4}"/>
+  <xr:revisionPtr revIDLastSave="245" documentId="11_284323B7179BCE7EC29A83AAEA162C28D842675C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46AF8565-8958-47B1-B7CD-DD894889BCB4}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="75">
   <si>
     <t>Día</t>
   </si>
@@ -135,9 +135,6 @@
   </si>
   <si>
     <t>Sí</t>
-  </si>
-  <si>
-    <t>En salsa de maracuyá</t>
   </si>
   <si>
     <t>Sopa de minestrone</t>
@@ -704,14 +701,14 @@
         <v>6</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F2" s="4"/>
     </row>
@@ -720,35 +717,33 @@
         <v>6</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>38</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F3" s="4"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -756,17 +751,17 @@
         <v>6</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>46</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -774,7 +769,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>37</v>
@@ -790,14 +785,14 @@
         <v>8</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F7" s="4"/>
     </row>
@@ -806,14 +801,14 @@
         <v>8</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F8" s="4"/>
     </row>
@@ -822,14 +817,14 @@
         <v>8</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F9" s="4"/>
     </row>
@@ -838,14 +833,14 @@
         <v>8</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F10" s="4"/>
     </row>
@@ -854,7 +849,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>9</v>
@@ -870,14 +865,14 @@
         <v>10</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F12" s="4"/>
     </row>
@@ -886,14 +881,14 @@
         <v>10</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F13" s="4"/>
     </row>
@@ -902,14 +897,14 @@
         <v>10</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F14" s="4"/>
     </row>
@@ -918,14 +913,14 @@
         <v>10</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F15" s="4"/>
     </row>
@@ -934,14 +929,14 @@
         <v>10</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F16" s="4"/>
     </row>
@@ -950,14 +945,14 @@
         <v>11</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F17" s="4"/>
     </row>
@@ -966,14 +961,14 @@
         <v>11</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F18" s="4"/>
     </row>
@@ -982,14 +977,14 @@
         <v>11</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F19" s="4"/>
     </row>
@@ -998,14 +993,14 @@
         <v>11</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F20" s="4"/>
     </row>
@@ -1014,7 +1009,7 @@
         <v>11</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>9</v>
@@ -1030,14 +1025,14 @@
         <v>12</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F22" s="4"/>
     </row>
@@ -1046,14 +1041,14 @@
         <v>12</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F23" s="4"/>
     </row>
@@ -1062,14 +1057,14 @@
         <v>12</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F24" s="4"/>
     </row>
@@ -1078,14 +1073,14 @@
         <v>12</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F25" s="4"/>
     </row>
@@ -1094,14 +1089,14 @@
         <v>12</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F26" s="4"/>
     </row>
@@ -1110,7 +1105,7 @@
         <v>13</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>9</v>
@@ -1130,7 +1125,7 @@
         <v>13</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>9</v>
@@ -1148,7 +1143,7 @@
         <v>13</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>9</v>
@@ -1166,7 +1161,7 @@
         <v>13</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>9</v>
@@ -1184,7 +1179,7 @@
         <v>13</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>9</v>
@@ -1202,7 +1197,7 @@
         <v>13</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>9</v>
@@ -1222,7 +1217,7 @@
         <v>13</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>9</v>
@@ -1231,7 +1226,7 @@
         <v>19</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F33" s="4"/>
     </row>
@@ -1240,7 +1235,7 @@
         <v>13</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>9</v>
@@ -1249,7 +1244,7 @@
         <v>19</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F34" s="4"/>
     </row>
@@ -1258,7 +1253,7 @@
         <v>13</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>9</v>
@@ -1276,14 +1271,14 @@
         <v>23</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F36" s="4"/>
     </row>
@@ -1292,14 +1287,14 @@
         <v>23</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D37" s="3"/>
       <c r="E37" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F37" s="4"/>
     </row>
@@ -1308,14 +1303,14 @@
         <v>23</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D38" s="3"/>
       <c r="E38" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F38" s="4"/>
     </row>
@@ -1324,14 +1319,14 @@
         <v>23</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F39" s="4"/>
     </row>
@@ -1340,14 +1335,14 @@
         <v>23</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D40" s="3"/>
       <c r="E40" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F40" s="4"/>
     </row>

--- a/menu-santaana.xlsx
+++ b/menu-santaana.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ce128a5e94e8105/Documents/Panadería Golconda/Menús/Menú en línea/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="245" documentId="11_284323B7179BCE7EC29A83AAEA162C28D842675C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46AF8565-8958-47B1-B7CD-DD894889BCB4}"/>
+  <xr:revisionPtr revIDLastSave="292" documentId="11_284323B7179BCE7EC29A83AAEA162C28D842675C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBC5ABAC-856F-4EC7-BE66-18F9DBF044B7}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Menú" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="73">
   <si>
     <t>Día</t>
   </si>
@@ -137,115 +137,109 @@
     <t>Sí</t>
   </si>
   <si>
-    <t>Sopa de minestrone</t>
-  </si>
-  <si>
-    <t>Ensalada cherry</t>
-  </si>
-  <si>
-    <t>17 ago</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crema de champiñones </t>
-  </si>
-  <si>
-    <t>Piccata de pollo</t>
-  </si>
-  <si>
-    <t>Pasta corta</t>
-  </si>
-  <si>
-    <t>Con tomates frescos</t>
-  </si>
-  <si>
-    <t>Ensalada de melón</t>
-  </si>
-  <si>
-    <t>Con vinagreta oriental</t>
-  </si>
-  <si>
-    <t>18 ago</t>
-  </si>
-  <si>
-    <t>Sopa de colicero</t>
-  </si>
-  <si>
-    <t>Churrasco a la plancha</t>
-  </si>
-  <si>
-    <t>Papa a la crema</t>
-  </si>
-  <si>
-    <t>Ensalada roja</t>
-  </si>
-  <si>
-    <t>19 ago</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sopa de verduras </t>
-  </si>
-  <si>
-    <t>Pollo a la hawaiana</t>
-  </si>
-  <si>
-    <t>Ensalada irlandesa</t>
-  </si>
-  <si>
-    <t>Arroz con ajonjolí</t>
-  </si>
-  <si>
-    <t>20 ago</t>
-  </si>
-  <si>
-    <t>21 ago</t>
-  </si>
-  <si>
-    <t>22 ago</t>
-  </si>
-  <si>
-    <t>Papa smiles</t>
-  </si>
-  <si>
-    <t>Sopa de sancocho</t>
-  </si>
-  <si>
-    <t>Pulpa de cerdo a la plancha</t>
-  </si>
-  <si>
-    <t>Papa criolla dorada</t>
-  </si>
-  <si>
-    <t>Sopa de tortilla de huevo</t>
-  </si>
-  <si>
-    <t>Mojarra frita</t>
-  </si>
-  <si>
-    <t>Patacón con hogao</t>
-  </si>
-  <si>
     <t>Ensalada con aguacate</t>
   </si>
   <si>
-    <t>Arroz con maicitos</t>
-  </si>
-  <si>
-    <t>Soufflé de papa</t>
-  </si>
-  <si>
-    <t>Ensalada del sol</t>
-  </si>
-  <si>
-    <t>23 ago</t>
-  </si>
-  <si>
-    <t>Pierna pernil al BBQ</t>
-  </si>
-  <si>
-    <t>Papa postiza</t>
-  </si>
-  <si>
-    <t>Ensalada César</t>
+    <t>24 ago</t>
+  </si>
+  <si>
+    <t>25 ago</t>
+  </si>
+  <si>
+    <t>26 ago</t>
+  </si>
+  <si>
+    <t>27 ago</t>
+  </si>
+  <si>
+    <t>28 ago</t>
+  </si>
+  <si>
+    <t>29 ago</t>
+  </si>
+  <si>
+    <t>30 ago</t>
+  </si>
+  <si>
+    <t>Sopa de mute</t>
+  </si>
+  <si>
+    <t>Sobrebarriga al horno</t>
+  </si>
+  <si>
+    <t>Papa chorreada</t>
+  </si>
+  <si>
+    <t>Sopa de lentejas</t>
+  </si>
+  <si>
+    <t>Pollo a la criolla</t>
+  </si>
+  <si>
+    <t>Torta de mazorca</t>
+  </si>
+  <si>
+    <t>Ensalada mixta a la vinagreta</t>
+  </si>
+  <si>
+    <t>Arroz con alverja</t>
+  </si>
+  <si>
+    <t>Crema de tomate</t>
+  </si>
+  <si>
+    <t>Tacos de carne desmechada</t>
+  </si>
+  <si>
+    <t>Fríjoles - Guacamole</t>
+  </si>
+  <si>
+    <t>Ensalada pico e gallo</t>
+  </si>
+  <si>
+    <t>Arroz amarillo</t>
+  </si>
+  <si>
+    <t>Sopa de patacón</t>
+  </si>
+  <si>
+    <t>Milanesa de pollo con ajonjolí</t>
+  </si>
+  <si>
+    <t>Papa al perejil</t>
+  </si>
+  <si>
+    <t>Verduras al gratín</t>
+  </si>
+  <si>
+    <t>Sopa de mazamorra chiquita</t>
+  </si>
+  <si>
+    <t>Soufflé de carne</t>
+  </si>
+  <si>
+    <t>Croqueta de yuca</t>
+  </si>
+  <si>
+    <t>Zanahorias y brócoli vicky</t>
+  </si>
+  <si>
+    <t>Papa en chupe</t>
+  </si>
+  <si>
+    <t>Aoufflé de verduras</t>
+  </si>
+  <si>
+    <t>Sopa de cascabeles</t>
+  </si>
+  <si>
+    <t>Goulash</t>
+  </si>
+  <si>
+    <t>Puré de papa</t>
+  </si>
+  <si>
+    <t>Habichuelas rancheras</t>
   </si>
 </sst>
 </file>
@@ -667,7 +661,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F45"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
@@ -676,7 +670,7 @@
     <col min="5" max="6" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -696,83 +690,79 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F2" s="4"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="4" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F3" s="4"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="4" t="s">
@@ -780,236 +770,236 @@
       </c>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F8" s="4"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F9" s="4"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F10" s="4"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="4" t="s">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="F11" s="4"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F12" s="4"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F13" s="4"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F14" s="4"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F15" s="4"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F16" s="4"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F17" s="4"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F18" s="4"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F19" s="4"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="4" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="F20" s="4"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>9</v>
@@ -1020,92 +1010,92 @@
       </c>
       <c r="F21" s="4"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F22" s="4"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F23" s="4"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F24" s="4"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F25" s="4"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="4" t="s">
-        <v>68</v>
+        <v>7</v>
       </c>
       <c r="F26" s="4"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>9</v>
@@ -1120,12 +1110,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>9</v>
@@ -1138,12 +1128,12 @@
       </c>
       <c r="F28" s="4"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>9</v>
@@ -1156,12 +1146,12 @@
       </c>
       <c r="F29" s="4"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>9</v>
@@ -1174,12 +1164,12 @@
       </c>
       <c r="F30" s="4"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>9</v>
@@ -1192,12 +1182,12 @@
       </c>
       <c r="F31" s="4"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>9</v>
@@ -1212,12 +1202,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>9</v>
@@ -1226,16 +1216,16 @@
         <v>19</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F33" s="4"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>9</v>
@@ -1244,16 +1234,16 @@
         <v>19</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F34" s="4"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>9</v>
@@ -1266,99 +1256,99 @@
       </c>
       <c r="F35" s="4"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="4" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="F36" s="4"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D37" s="3"/>
       <c r="E37" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F37" s="4"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D38" s="3"/>
       <c r="E38" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F38" s="4"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F39" s="4"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>37</v>
       </c>
       <c r="D40" s="3"/>
       <c r="E40" s="4" t="s">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="F40" s="4"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B41" s="8"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B42" s="8"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B43" s="8"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B44" s="8"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B45" s="8"/>
     </row>
   </sheetData>
@@ -1381,84 +1371,84 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="6"/>
     </row>
-    <row r="3" spans="1:1" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" s="6"/>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" s="6"/>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" s="6"/>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
         <v>36</v>
       </c>

--- a/menu-santaana.xlsx
+++ b/menu-santaana.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ce128a5e94e8105/Documents/Panadería Golconda/Menús/Menú en línea/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="292" documentId="11_284323B7179BCE7EC29A83AAEA162C28D842675C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBC5ABAC-856F-4EC7-BE66-18F9DBF044B7}"/>
+  <xr:revisionPtr revIDLastSave="357" documentId="11_284323B7179BCE7EC29A83AAEA162C28D842675C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1213E58A-A316-4B5C-922E-0568B4EFADE9}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Menú" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="79">
   <si>
     <t>Día</t>
   </si>
@@ -140,106 +140,124 @@
     <t>Ensalada con aguacate</t>
   </si>
   <si>
-    <t>24 ago</t>
-  </si>
-  <si>
-    <t>25 ago</t>
-  </si>
-  <si>
-    <t>26 ago</t>
-  </si>
-  <si>
-    <t>27 ago</t>
-  </si>
-  <si>
-    <t>28 ago</t>
-  </si>
-  <si>
-    <t>29 ago</t>
-  </si>
-  <si>
-    <t>30 ago</t>
-  </si>
-  <si>
-    <t>Sopa de mute</t>
-  </si>
-  <si>
-    <t>Sobrebarriga al horno</t>
-  </si>
-  <si>
-    <t>Papa chorreada</t>
-  </si>
-  <si>
-    <t>Sopa de lentejas</t>
-  </si>
-  <si>
-    <t>Pollo a la criolla</t>
-  </si>
-  <si>
-    <t>Torta de mazorca</t>
-  </si>
-  <si>
-    <t>Ensalada mixta a la vinagreta</t>
-  </si>
-  <si>
-    <t>Arroz con alverja</t>
-  </si>
-  <si>
-    <t>Crema de tomate</t>
-  </si>
-  <si>
-    <t>Tacos de carne desmechada</t>
-  </si>
-  <si>
-    <t>Fríjoles - Guacamole</t>
-  </si>
-  <si>
-    <t>Ensalada pico e gallo</t>
-  </si>
-  <si>
-    <t>Arroz amarillo</t>
-  </si>
-  <si>
-    <t>Sopa de patacón</t>
-  </si>
-  <si>
-    <t>Milanesa de pollo con ajonjolí</t>
-  </si>
-  <si>
-    <t>Papa al perejil</t>
-  </si>
-  <si>
-    <t>Verduras al gratín</t>
-  </si>
-  <si>
-    <t>Sopa de mazamorra chiquita</t>
-  </si>
-  <si>
-    <t>Soufflé de carne</t>
-  </si>
-  <si>
-    <t>Croqueta de yuca</t>
-  </si>
-  <si>
-    <t>Zanahorias y brócoli vicky</t>
-  </si>
-  <si>
-    <t>Papa en chupe</t>
-  </si>
-  <si>
-    <t>Aoufflé de verduras</t>
-  </si>
-  <si>
-    <t>Sopa de cascabeles</t>
-  </si>
-  <si>
-    <t>Goulash</t>
-  </si>
-  <si>
-    <t>Puré de papa</t>
-  </si>
-  <si>
-    <t>Habichuelas rancheras</t>
+    <t>31 ago</t>
+  </si>
+  <si>
+    <t>1 sept</t>
+  </si>
+  <si>
+    <t>2 sept</t>
+  </si>
+  <si>
+    <t>3 sept</t>
+  </si>
+  <si>
+    <t>4 sept</t>
+  </si>
+  <si>
+    <t>5 sept</t>
+  </si>
+  <si>
+    <t>6 sept</t>
+  </si>
+  <si>
+    <t>Sopa de mazorca</t>
+  </si>
+  <si>
+    <t>Carne a la cerveza</t>
+  </si>
+  <si>
+    <t>Cascos de papa dorada</t>
+  </si>
+  <si>
+    <t>Ensalada del sol</t>
+  </si>
+  <si>
+    <t>Arroz al cebollín</t>
+  </si>
+  <si>
+    <t>Sopa de pasta</t>
+  </si>
+  <si>
+    <t>Arroz con pollo</t>
+  </si>
+  <si>
+    <t>Plátano al horno con queso y bocadillo</t>
+  </si>
+  <si>
+    <t>Ensalada al huevo</t>
+  </si>
+  <si>
+    <t>Bandeja paisa</t>
+  </si>
+  <si>
+    <t>9 acompañamientos</t>
+  </si>
+  <si>
+    <t>Sopa de arracacha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carne molina, chicharrón, chorizo, fríjoles, huevo, plátano, aguacate, arepa y arroz blanco </t>
+  </si>
+  <si>
+    <t>Monedas de plátano con queso</t>
+  </si>
+  <si>
+    <t>Ensalada bellavista</t>
+  </si>
+  <si>
+    <t>Sopa de avena</t>
+  </si>
+  <si>
+    <t>Pechuga rellena</t>
+  </si>
+  <si>
+    <t>Con jamón y queso</t>
+  </si>
+  <si>
+    <t>Papa duquesa</t>
+  </si>
+  <si>
+    <t>Ensalada mil islas</t>
+  </si>
+  <si>
+    <t>Arroz malteado</t>
+  </si>
+  <si>
+    <t>Sopa de colicero</t>
+  </si>
+  <si>
+    <t>Filete de mojarra</t>
+  </si>
+  <si>
+    <t>En salsa de camarones</t>
+  </si>
+  <si>
+    <t>Enyucado</t>
+  </si>
+  <si>
+    <t>Arroz palito</t>
+  </si>
+  <si>
+    <t>Yuca dorada</t>
+  </si>
+  <si>
+    <t>Sidra en salsa al pimentón</t>
+  </si>
+  <si>
+    <t>Crema de zuchinni</t>
+  </si>
+  <si>
+    <t>Pollo oriental</t>
+  </si>
+  <si>
+    <t>En salsa de mango</t>
+  </si>
+  <si>
+    <t>Copos de papa con ajonjolí</t>
+  </si>
+  <si>
+    <t>Ensalada mediterránea</t>
   </si>
 </sst>
 </file>
@@ -660,7 +678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -750,7 +768,7 @@
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="4" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="F5" s="4"/>
     </row>
@@ -766,7 +784,7 @@
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="4" t="s">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="F6" s="4"/>
     </row>
@@ -782,7 +800,7 @@
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F7" s="4"/>
     </row>
@@ -798,7 +816,7 @@
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F8" s="4"/>
     </row>
@@ -814,7 +832,7 @@
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F9" s="4"/>
     </row>
@@ -830,7 +848,7 @@
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F10" s="4"/>
     </row>
@@ -845,9 +863,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="3"/>
-      <c r="E11" s="4" t="s">
-        <v>53</v>
-      </c>
+      <c r="E11" s="4"/>
       <c r="F11" s="4"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
@@ -860,13 +876,15 @@
       <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="3"/>
+      <c r="D12" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="E12" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F12" s="4"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" ht="42" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>10</v>
       </c>
@@ -876,11 +894,15 @@
       <c r="C13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="3"/>
+      <c r="D13" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="E13" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F13" s="4"/>
+        <v>56</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
@@ -892,10 +914,10 @@
       <c r="C14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="4" t="s">
-        <v>56</v>
-      </c>
+      <c r="D14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="4"/>
       <c r="F14" s="4"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
@@ -908,10 +930,10 @@
       <c r="C15" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="D15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="4"/>
       <c r="F15" s="4"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
@@ -924,87 +946,99 @@
       <c r="C16" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="4" t="s">
-        <v>58</v>
-      </c>
+      <c r="D16" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="4"/>
       <c r="F16" s="4"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D17" s="3"/>
+      <c r="D17" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="E17" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F17" s="4"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D18" s="3"/>
+      <c r="D18" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="E18" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F18" s="4"/>
+        <v>21</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D19" s="3"/>
+      <c r="D19" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="E19" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F19" s="4"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="3"/>
+      <c r="D20" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="E20" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F20" s="4"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D21" s="3"/>
+      <c r="D21" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="E21" s="4" t="s">
         <v>7</v>
       </c>
@@ -1012,173 +1046,165 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F22" s="4"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="F23" s="4"/>
+        <v>62</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F24" s="4"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F25" s="4"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="4" t="s">
-        <v>7</v>
+        <v>66</v>
       </c>
       <c r="F26" s="4"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>14</v>
-      </c>
+      <c r="D27" s="3"/>
       <c r="E27" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>16</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="F27" s="4"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>14</v>
-      </c>
+      <c r="D28" s="3"/>
       <c r="E28" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F28" s="4"/>
+        <v>68</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>14</v>
-      </c>
+      <c r="D29" s="3"/>
       <c r="E29" s="4" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="F29" s="4"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>14</v>
-      </c>
+      <c r="D30" s="3"/>
       <c r="E30" s="4" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="F30" s="4"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>19</v>
-      </c>
+      <c r="D31" s="3"/>
       <c r="E31" s="4" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="F31" s="4"/>
     </row>
@@ -1193,13 +1219,13 @@
         <v>9</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
@@ -1213,10 +1239,10 @@
         <v>9</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="F33" s="4"/>
     </row>
@@ -1231,10 +1257,10 @@
         <v>9</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="F34" s="4"/>
     </row>
@@ -1249,7 +1275,7 @@
         <v>9</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>7</v>
@@ -1258,109 +1284,203 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D36" s="3"/>
+        <v>9</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="E36" s="4" t="s">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="F36" s="4"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D37" s="3"/>
+        <v>9</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="E37" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="F37" s="4"/>
+        <v>21</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D38" s="3"/>
+        <v>9</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="E38" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F38" s="4"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D39" s="3"/>
+        <v>9</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="E39" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F39" s="4"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D40" s="3"/>
+        <v>9</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="E40" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F40" s="4"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B41" s="8"/>
+      <c r="A41" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D41" s="3"/>
+      <c r="E41" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F41" s="4"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B42" s="8"/>
+      <c r="A42" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D42" s="3"/>
+      <c r="E42" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B43" s="8"/>
+      <c r="A43" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D43" s="3"/>
+      <c r="E43" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F43" s="4"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B44" s="8"/>
+      <c r="A44" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D44" s="3"/>
+      <c r="E44" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F44" s="4"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B45" s="8"/>
+      <c r="A45" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D45" s="3"/>
+      <c r="E45" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F45" s="4"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B46" s="8"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B47" s="8"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B48" s="8"/>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B49" s="8"/>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B50" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="A2:A400" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="A2:A405" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C2:C400" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C2:C405" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Sí,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D400" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D405" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Opción 1,Opción 2,Opción 3"</formula1>
     </dataValidation>
   </dataValidations>
